--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,90 +523,25 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>HT_Odd_Over25</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>HT_Odd_Under25</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>FT_Odd_Over05</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over15</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under15</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over25</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under25</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over35</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under35</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_Yes</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_No</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_D</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_A_D</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -688,46 +623,7 @@
       <c r="U2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="3" t="n">
+      <c r="V2" s="3" t="n">
         <v>46014.21875</v>
       </c>
     </row>
@@ -807,46 +703,7 @@
       <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="3" t="n">
+      <c r="V3" s="3" t="n">
         <v>46014.22916666666</v>
       </c>
     </row>
@@ -926,46 +783,7 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="3" t="n">
+      <c r="V4" s="3" t="n">
         <v>46014.375</v>
       </c>
     </row>
@@ -1045,46 +863,7 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="3" t="n">
+      <c r="V5" s="3" t="n">
         <v>46014.38541666666</v>
       </c>
     </row>
@@ -1164,46 +943,7 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="3" t="n">
+      <c r="V6" s="3" t="n">
         <v>46014.41666666666</v>
       </c>
     </row>
@@ -1283,46 +1023,7 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="3" t="n">
+      <c r="V7" s="3" t="n">
         <v>46014.41666666666</v>
       </c>
     </row>
@@ -1402,46 +1103,7 @@
       <c r="U8" t="n">
         <v>0</v>
       </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="3" t="n">
+      <c r="V8" s="3" t="n">
         <v>46014.58333333334</v>
       </c>
     </row>
@@ -1510,10 +1172,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1521,46 +1183,7 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="3" t="n">
+      <c r="V9" s="3" t="n">
         <v>46014.73958333334</v>
       </c>
     </row>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,25 +523,90 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>HT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under05</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over15</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under15</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over25</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under25</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>FT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over15</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under15</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over35</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under35</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_H_D</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_A_D</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -623,7 +688,46 @@
       <c r="U2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="3" t="n">
         <v>46014.21875</v>
       </c>
     </row>
@@ -703,7 +807,46 @@
       <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="3" t="n">
         <v>46014.22916666666</v>
       </c>
     </row>
@@ -783,7 +926,46 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
         <v>46014.375</v>
       </c>
     </row>
@@ -863,7 +1045,46 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>46014.38541666666</v>
       </c>
     </row>
@@ -888,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -943,7 +1164,46 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="3" t="n">
         <v>46014.41666666666</v>
       </c>
     </row>
@@ -968,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1023,7 +1283,46 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="n">
         <v>46014.41666666666</v>
       </c>
     </row>
@@ -1103,7 +1402,46 @@
       <c r="U8" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="n">
         <v>46014.58333333334</v>
       </c>
     </row>
@@ -1172,18 +1510,57 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
         <v>1.68</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AB9" t="n">
         <v>2.05</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="n">
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="n">
         <v>46014.73958333334</v>
       </c>
     </row>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1442,125 +1442,6 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46014.58333333334</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>46014</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Portugal Liga NOS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Vitória Guimarães</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Sporting CP</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="3" t="n">
         <v>46014.73958333334</v>
       </c>
     </row>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1332,116 +1332,235 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MC Alger</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ben Aknoun</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="n">
+        <v>46014.64583333334</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Portugal Liga NOS</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Vitória Guimarães</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Sporting CP</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M9" t="n">
         <v>4.3</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N9" t="n">
         <v>1.4</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
         <v>1.68</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AB9" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="3" t="n">
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="n">
         <v>46014.73958333334</v>
       </c>
     </row>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.65</v>
       </c>
-      <c r="M2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46014.21875</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
         <v>2.1</v>
@@ -704,10 +704,10 @@
         <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC2" t="n">
         <v>2.7</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O2" t="n">
         <v>2.1</v>
@@ -683,43 +683,43 @@
         <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
         <v>1.49</v>
       </c>
       <c r="V2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC2" t="n">
         <v>2.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
         <v>1.25</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46014.22916666666</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46014.375</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
         <v>2.1</v>
@@ -704,10 +704,10 @@
         <v>3.94</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC2" t="n">
         <v>2.7</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46014.73958333334</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -668,10 +668,10 @@
         <v>4.8</v>
       </c>
       <c r="O2" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="n">
         <v>4.75</v>
@@ -695,13 +695,13 @@
         <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
         <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="AA2" t="n">
         <v>1.7</v>
@@ -713,7 +713,7 @@
         <v>2.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
         <v>1.67</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>3.71</v>
       </c>
       <c r="O3" t="n">
         <v>2.45</v>
@@ -799,25 +799,25 @@
         <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="T3" t="n">
         <v>2.67</v>
       </c>
       <c r="U3" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
         <v>6.65</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
         <v>3.34</v>
@@ -900,7 +900,7 @@
         <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -939,7 +939,7 @@
         <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
         <v>2.11</v>
@@ -957,13 +957,13 @@
         <v>1.83</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
         <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46014.375</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1492,25 +1492,25 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
         <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
         <v>2.89</v>
@@ -1519,13 +1519,13 @@
         <v>2.69</v>
       </c>
       <c r="U9" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
         <v>1.05</v>
@@ -1534,16 +1534,16 @@
         <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AD9" t="n">
         <v>1.33</v>
@@ -1555,7 +1555,7 @@
         <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
         <v>1.06</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
         <v>4.8</v>
@@ -671,13 +671,13 @@
         <v>2.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
         <v>4.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
         <v>3.1</v>
@@ -686,10 +686,10 @@
         <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="V2" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W2" t="n">
         <v>1.08</v>
@@ -698,25 +698,25 @@
         <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
@@ -796,7 +796,7 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
         <v>2.79</v>
@@ -811,7 +811,7 @@
         <v>6.65</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
         <v>1.05</v>
@@ -826,13 +826,13 @@
         <v>1.84</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>3.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
         <v>1.72</v>
@@ -841,10 +841,10 @@
         <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46014.22916666666</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="M4" t="n">
         <v>3.25</v>
@@ -921,7 +921,7 @@
         <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="U4" t="n">
         <v>1.31</v>
@@ -933,7 +933,7 @@
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
         <v>1.31</v>
@@ -945,13 +945,13 @@
         <v>2.11</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC4" t="n">
         <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
         <v>1.83</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
         <v>4.8</v>
@@ -704,10 +704,10 @@
         <v>3.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC2" t="n">
         <v>2.9</v>
@@ -1504,10 +1504,10 @@
         <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
@@ -1516,13 +1516,13 @@
         <v>2.89</v>
       </c>
       <c r="T9" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="U9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.08</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="O2" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="Q2" t="n">
         <v>4.75</v>
@@ -680,34 +680,34 @@
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="U2" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
         <v>2.9</v>
@@ -781,7 +781,7 @@
         <v>1.92</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
         <v>3.71</v>
@@ -796,7 +796,7 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
         <v>2.79</v>
@@ -811,10 +811,10 @@
         <v>6.65</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
         <v>1.25</v>
@@ -832,16 +832,16 @@
         <v>3.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
         <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
         <v>1.83</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
         <v>3.25</v>
@@ -906,13 +906,13 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="P4" t="n">
         <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
       <c r="R4" t="n">
         <v>1.41</v>
@@ -921,13 +921,13 @@
         <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>3.12</v>
+        <v>2.97</v>
       </c>
       <c r="U4" t="n">
         <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
@@ -951,19 +951,19 @@
         <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
         <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46014.375</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>7.65</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>4.67</v>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O9" t="n">
         <v>6</v>
@@ -1537,10 +1537,10 @@
         <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
         <v>3.14</v>
@@ -1555,10 +1555,10 @@
         <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46014.73958333334</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
         <v>2.1</v>
@@ -704,10 +704,10 @@
         <v>3.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC2" t="n">
         <v>2.9</v>
@@ -1492,19 +1492,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.65</v>
+        <v>7.4</v>
       </c>
       <c r="M9" t="n">
-        <v>4.67</v>
+        <v>4.8</v>
       </c>
       <c r="N9" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="O9" t="n">
         <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="Q9" t="n">
         <v>1.89</v>
@@ -1516,16 +1516,16 @@
         <v>2.89</v>
       </c>
       <c r="T9" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="U9" t="n">
         <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
         <v>1.05</v>
@@ -1543,7 +1543,7 @@
         <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
         <v>1.33</v>
@@ -1555,7 +1555,7 @@
         <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>2.8</v>
       </c>
       <c r="AH9" t="n">
         <v>1.07</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
         <v>6</v>
@@ -1537,10 +1537,10 @@
         <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
         <v>3.1</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -671,37 +671,37 @@
         <v>2.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
         <v>4.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="T2" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="U2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V2" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="W2" t="n">
         <v>1.07</v>
       </c>
       <c r="X2" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AA2" t="n">
         <v>1.7</v>
@@ -710,19 +710,19 @@
         <v>2.02</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH2" t="n">
         <v>2.15</v>
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
         <v>3.71</v>
@@ -790,7 +790,7 @@
         <v>2.45</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
@@ -805,7 +805,7 @@
         <v>2.67</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V3" t="n">
         <v>6.65</v>
@@ -820,7 +820,7 @@
         <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA3" t="n">
         <v>1.84</v>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -909,10 +909,10 @@
         <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.84</v>
+        <v>3.68</v>
       </c>
       <c r="R4" t="n">
         <v>1.41</v>
@@ -936,13 +936,13 @@
         <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z4" t="n">
         <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AB4" t="n">
         <v>1.67</v>
@@ -951,19 +951,19 @@
         <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
         <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46014.375</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1382,40 +1382,40 @@
         <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
         <v>2.07</v>
@@ -1424,22 +1424,22 @@
         <v>1.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46014.64583333334</v>
@@ -1504,13 +1504,13 @@
         <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
         <v>1.89</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
         <v>2.89</v>
@@ -1522,7 +1522,7 @@
         <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.05</v>
@@ -1531,10 +1531,10 @@
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AA9" t="n">
         <v>1.68</v>
@@ -1543,10 +1543,10 @@
         <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -1555,10 +1555,10 @@
         <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46014.73958333334</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
         <v>4.8</v>
@@ -671,13 +671,13 @@
         <v>2.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
         <v>2.99</v>
@@ -695,19 +695,19 @@
         <v>1.07</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
         <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.7</v>
+        <v>4.09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
         <v>2.76</v>
@@ -716,16 +716,16 @@
         <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46014.21875</v>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
         <v>3.4</v>
@@ -796,7 +796,7 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
         <v>2.79</v>
@@ -820,7 +820,7 @@
         <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA3" t="n">
         <v>1.84</v>
@@ -838,7 +838,7 @@
         <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AG3" t="n">
         <v>1.3</v>
@@ -903,7 +903,7 @@
         <v>3.22</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
         <v>2.88</v>
@@ -945,13 +945,13 @@
         <v>2.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
         <v>3.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE4" t="n">
         <v>1.83</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M8" t="n">
         <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O8" t="n">
         <v>1.85</v>
@@ -1418,10 +1418,10 @@
         <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
         <v>3.5</v>
@@ -1430,7 +1430,7 @@
         <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="AF8" t="n">
         <v>1.38</v>
@@ -1439,7 +1439,7 @@
         <v>1.14</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46014.64583333334</v>
@@ -1492,25 +1492,25 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>4.56</v>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
         <v>2.89</v>
@@ -1522,7 +1522,7 @@
         <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="W9" t="n">
         <v>1.05</v>
@@ -1537,10 +1537,10 @@
         <v>3.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
         <v>3.14</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
         <v>4.8</v>
@@ -704,10 +704,10 @@
         <v>4.09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC2" t="n">
         <v>2.76</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
         <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="T8" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46014.64583333334</v>
@@ -1498,7 +1498,7 @@
         <v>4.56</v>
       </c>
       <c r="N9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="O9" t="n">
         <v>6.5</v>
@@ -1507,7 +1507,7 @@
         <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
@@ -1534,7 +1534,7 @@
         <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.86</v>
@@ -1543,7 +1543,7 @@
         <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="AD9" t="n">
         <v>1.3</v>
@@ -1555,7 +1555,7 @@
         <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.72</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
         <v>1.1</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>4.56</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
         <v>6.5</v>
@@ -1537,10 +1537,10 @@
         <v>3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
         <v>3.15</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -671,16 +671,16 @@
         <v>2.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="T2" t="n">
         <v>2.56</v>
@@ -701,7 +701,7 @@
         <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.09</v>
+        <v>3.8</v>
       </c>
       <c r="AA2" t="n">
         <v>1.7</v>
@@ -713,19 +713,19 @@
         <v>2.76</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AF2" t="n">
         <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46014.21875</v>
@@ -1382,22 +1382,22 @@
         <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="U8" t="n">
         <v>1.28</v>
@@ -1406,7 +1406,7 @@
         <v>9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
@@ -1415,7 +1415,7 @@
         <v>1.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AA8" t="n">
         <v>2.07</v>
@@ -1424,22 +1424,22 @@
         <v>1.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46014.64583333334</v>
@@ -1507,7 +1507,7 @@
         <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
@@ -1519,7 +1519,7 @@
         <v>2.73</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
         <v>6.1</v>
@@ -1543,7 +1543,7 @@
         <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="AD9" t="n">
         <v>1.3</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -784,7 +784,7 @@
         <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
         <v>2.45</v>
@@ -796,16 +796,16 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
         <v>2.79</v>
       </c>
       <c r="T3" t="n">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="U3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
         <v>6.65</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M4" t="n">
         <v>3.22</v>
@@ -909,7 +909,7 @@
         <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
         <v>3.68</v>
@@ -936,7 +936,7 @@
         <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
         <v>3</v>
@@ -945,7 +945,7 @@
         <v>2.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC4" t="n">
         <v>3.58</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -784,13 +784,13 @@
         <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>3.79</v>
       </c>
       <c r="O3" t="n">
         <v>2.45</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
@@ -808,13 +808,13 @@
         <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
         <v>1.25</v>
@@ -823,13 +823,13 @@
         <v>3.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AD3" t="n">
         <v>1.3</v>
@@ -838,7 +838,7 @@
         <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
         <v>1.3</v>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
         <v>3.05</v>
@@ -921,7 +921,7 @@
         <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>2.97</v>
+        <v>3.18</v>
       </c>
       <c r="U4" t="n">
         <v>1.31</v>
@@ -939,13 +939,13 @@
         <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA4" t="n">
         <v>2.06</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AC4" t="n">
         <v>3.58</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -680,7 +680,7 @@
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
         <v>2.56</v>
@@ -698,7 +698,7 @@
         <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
         <v>3.8</v>
@@ -716,7 +716,7 @@
         <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
         <v>1.95</v>
@@ -725,7 +725,7 @@
         <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46014.21875</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1186,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1382,19 +1382,19 @@
         <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="P8" t="n">
         <v>2.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
         <v>3.18</v>
@@ -1406,7 +1406,7 @@
         <v>9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
@@ -1424,16 +1424,16 @@
         <v>1.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD8" t="n">
         <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG8" t="n">
         <v>1.18</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="O9" t="n">
         <v>6.5</v>
@@ -1507,10 +1507,10 @@
         <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
         <v>2.89</v>
@@ -1519,7 +1519,7 @@
         <v>2.73</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
         <v>6.1</v>
@@ -1534,19 +1534,19 @@
         <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="O2" t="n">
         <v>2.1</v>
@@ -677,37 +677,37 @@
         <v>4.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
         <v>2.56</v>
       </c>
       <c r="U2" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="V2" t="n">
         <v>5.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
         <v>3.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
         <v>2.76</v>
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="M3" t="n">
         <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>3.79</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
         <v>2.45</v>
       </c>
       <c r="P3" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
@@ -802,10 +802,10 @@
         <v>2.79</v>
       </c>
       <c r="T3" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V3" t="n">
         <v>6.75</v>
@@ -814,7 +814,7 @@
         <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
         <v>1.25</v>
@@ -826,7 +826,7 @@
         <v>1.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>3.08</v>
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>2.54</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.68</v>
+        <v>3.44</v>
       </c>
       <c r="R4" t="n">
         <v>1.41</v>
@@ -921,7 +921,7 @@
         <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="U4" t="n">
         <v>1.31</v>
@@ -939,13 +939,13 @@
         <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC4" t="n">
         <v>3.58</v>
@@ -1016,55 +1016,55 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="M5" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC5" t="n">
         <v>2.2</v>
@@ -1073,16 +1073,16 @@
         <v>1.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46014.38541666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.8</v>
+        <v>1.59</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="N6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.38</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46014.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.55</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>4.33</v>
+        <v>5.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.54</v>
+        <v>1.28</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46014.41666666666</v>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="P8" t="n">
         <v>2.01</v>
@@ -1391,13 +1391,13 @@
         <v>9.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="T8" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="U8" t="n">
         <v>1.28</v>
@@ -1418,10 +1418,10 @@
         <v>2.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
         <v>4.2</v>
@@ -1430,16 +1430,16 @@
         <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG8" t="n">
         <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46014.64583333334</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
         <v>2.1</v>
@@ -704,10 +704,10 @@
         <v>3.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC2" t="n">
         <v>2.76</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="P5" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
         <v>1.22</v>
@@ -1040,10 +1040,10 @@
         <v>3.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V5" t="n">
         <v>4.3</v>
@@ -1058,13 +1058,13 @@
         <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AC5" t="n">
         <v>2.2</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.59</v>
+        <v>5.8</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>1.38</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>7.17</v>
       </c>
       <c r="P6" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.55</v>
+        <v>1.72</v>
       </c>
       <c r="R6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
         <v>4.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="U6" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="AA6" t="n">
         <v>1.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.97</v>
+        <v>3.21</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.77</v>
+        <v>2.14</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.13</v>
+        <v>3.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.22</v>
+        <v>1.06</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46014.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>8.300000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="M7" t="n">
-        <v>5.05</v>
+        <v>4.4</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>5.5</v>
+        <v>1.98</v>
       </c>
       <c r="P7" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.72</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="U7" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="V7" t="n">
         <v>3.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.85</v>
+        <v>6.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.19</v>
+        <v>2.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.02</v>
+        <v>2.22</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46014.41666666666</v>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
         <v>1.95</v>
       </c>
       <c r="P8" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="U8" t="n">
         <v>1.28</v>
@@ -1406,7 +1406,7 @@
         <v>9</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
@@ -1415,13 +1415,13 @@
         <v>1.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC8" t="n">
         <v>4.2</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
         <v>6.5</v>
@@ -1507,10 +1507,10 @@
         <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
         <v>2.89</v>
@@ -1537,13 +1537,13 @@
         <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.13</v>
+        <v>3.21</v>
       </c>
       <c r="AD9" t="n">
         <v>1.33</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -671,31 +671,31 @@
         <v>2.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="Q2" t="n">
         <v>4.75</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="T2" t="n">
         <v>2.56</v>
       </c>
       <c r="U2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="V2" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
         <v>1.2</v>
@@ -725,7 +725,7 @@
         <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46014.21875</v>
@@ -1025,40 +1025,40 @@
         <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.72</v>
+        <v>2.57</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.05</v>
+        <v>4.65</v>
       </c>
       <c r="AA5" t="n">
         <v>1.48</v>
@@ -1073,16 +1073,16 @@
         <v>1.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46014.38541666666</v>
@@ -1144,40 +1144,40 @@
         <v>1.38</v>
       </c>
       <c r="O6" t="n">
-        <v>7.17</v>
+        <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="V6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA6" t="n">
         <v>1.3</v>
@@ -1192,16 +1192,16 @@
         <v>1.82</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.14</v>
+        <v>1.69</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.2</v>
+        <v>1.06</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46014.41666666666</v>
@@ -1263,40 +1263,40 @@
         <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="P7" t="n">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="Q7" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V7" t="n">
         <v>4</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V7" t="n">
-        <v>3.6</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.75</v>
+        <v>5.65</v>
       </c>
       <c r="AA7" t="n">
         <v>1.3</v>
@@ -1311,16 +1311,16 @@
         <v>1.85</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46014.41666666666</v>
@@ -1388,13 +1388,13 @@
         <v>2.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
       <c r="R8" t="n">
         <v>1.48</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="T8" t="n">
         <v>3.18</v>
@@ -1412,10 +1412,10 @@
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AA8" t="n">
         <v>2.07</v>
@@ -1424,7 +1424,7 @@
         <v>1.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AD8" t="n">
         <v>1.18</v>
@@ -1436,10 +1436,10 @@
         <v>1.43</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46014.64583333334</v>
@@ -1510,31 +1510,31 @@
         <v>1.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.89</v>
+        <v>3.02</v>
       </c>
       <c r="T9" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V9" t="n">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
         <v>1.68</v>
@@ -1543,16 +1543,16 @@
         <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.21</v>
+        <v>2.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
         <v>1.2</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>3.79</v>
       </c>
       <c r="O3" t="n">
         <v>2.45</v>
@@ -796,40 +796,40 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>2.79</v>
+        <v>3.06</v>
       </c>
       <c r="T3" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="U3" t="n">
         <v>1.41</v>
       </c>
       <c r="V3" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="W3" t="n">
         <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
         <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD3" t="n">
         <v>1.3</v>
@@ -838,7 +838,7 @@
         <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
         <v>1.3</v>
@@ -897,34 +897,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
         <v>2.54</v>
       </c>
       <c r="O4" t="n">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>3.23</v>
+        <v>3.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
         <v>7.8</v>
@@ -933,22 +933,22 @@
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AD4" t="n">
         <v>1.22</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -761,20 +761,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.6</v>
+        <v>3.23</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="O4" t="n">
         <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="T4" t="n">
-        <v>3.04</v>
+        <v>3.23</v>
       </c>
       <c r="U4" t="n">
         <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
@@ -936,13 +936,13 @@
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
         <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
         <v>1.67</v>
@@ -957,13 +957,13 @@
         <v>1.83</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46014.375</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.8</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="N6" t="n">
-        <v>1.38</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>2.01</v>
       </c>
       <c r="P6" t="n">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.57</v>
+        <v>5.24</v>
       </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S6" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="AA6" t="n">
         <v>1.3</v>
@@ -1186,22 +1186,22 @@
         <v>3.21</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.69</v>
+        <v>2.38</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46014.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,49 +1254,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.53</v>
+        <v>5.8</v>
       </c>
       <c r="M7" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>1.38</v>
       </c>
       <c r="O7" t="n">
-        <v>2.01</v>
+        <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>2.47</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.24</v>
+        <v>1.57</v>
       </c>
       <c r="R7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V7" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA7" t="n">
         <v>1.3</v>
@@ -1305,22 +1305,22 @@
         <v>3.21</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.38</v>
+        <v>1.69</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46014.41666666666</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -999,90 +999,90 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="M5" t="n">
         <v>3.85</v>
       </c>
       <c r="N5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2.5</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.57</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
         <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
         <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AG5" t="n">
         <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46014.38541666666</v>
@@ -1118,57 +1118,57 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
         <v>1.53</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="P6" t="n">
         <v>2.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.24</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
@@ -1177,31 +1177,31 @@
         <v>1.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.65</v>
+        <v>6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.21</v>
+        <v>2.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AG6" t="n">
         <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46014.41666666666</v>
@@ -1237,57 +1237,57 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="M7" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O7" t="n">
+        <v>11</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S7" t="n">
         <v>4.7</v>
       </c>
-      <c r="N7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="O7" t="n">
-        <v>10</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4.2</v>
-      </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
@@ -1302,25 +1302,25 @@
         <v>1.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
         <v>1.69</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46014.41666666666</v>
@@ -1382,19 +1382,19 @@
         <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="P8" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="R8" t="n">
         <v>1.48</v>
       </c>
       <c r="S8" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
         <v>3.18</v>
@@ -1403,7 +1403,7 @@
         <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="W8" t="n">
         <v>1.05</v>
@@ -1412,7 +1412,7 @@
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
         <v>2.7</v>
@@ -1424,22 +1424,22 @@
         <v>1.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46014.64583333334</v>
@@ -1501,40 +1501,40 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="P9" t="n">
         <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="U9" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="V9" t="n">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="n">
         <v>1.68</v>
@@ -1543,22 +1543,22 @@
         <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46014.73958333334</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1124,7 +1124,7 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.53</v>
+        <v>14</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>1.28</v>
       </c>
       <c r="O6" t="n">
-        <v>1.96</v>
+        <v>11</v>
       </c>
       <c r="P6" t="n">
-        <v>2.47</v>
+        <v>2.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>1.49</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="V6" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AD6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.69</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.33</v>
+        <v>1.03</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46014.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1243,7 +1243,7 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>14</v>
+        <v>1.53</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>11</v>
+        <v>1.96</v>
       </c>
       <c r="P7" t="n">
-        <v>2.81</v>
+        <v>2.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.49</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="S7" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="U7" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="V7" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.03</v>
+        <v>1.69</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.03</v>
+        <v>2.33</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46014.41666666666</v>
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
         <v>1.94</v>
       </c>
       <c r="P8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
         <v>9</v>
@@ -1394,10 +1394,10 @@
         <v>1.48</v>
       </c>
       <c r="S8" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
         <v>1.28</v>
@@ -1406,40 +1406,40 @@
         <v>7.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
         <v>4.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46014.64583333334</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O9" t="n">
         <v>6</v>
@@ -1510,43 +1510,43 @@
         <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="T9" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="V9" t="n">
         <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE9" t="n">
         <v>1.95</v>

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">

--- a/jogos_2025-12-23.xlsx
+++ b/jogos_2025-12-23.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1124,7 +1124,7 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>1.28</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>1.96</v>
       </c>
       <c r="P6" t="n">
-        <v>2.81</v>
+        <v>2.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.49</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.03</v>
+        <v>1.69</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.03</v>
+        <v>2.33</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46014.41666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1243,7 +1243,7 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.53</v>
+        <v>14</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>1.28</v>
       </c>
       <c r="O7" t="n">
-        <v>1.96</v>
+        <v>11</v>
       </c>
       <c r="P7" t="n">
-        <v>2.47</v>
+        <v>2.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>1.49</v>
       </c>
       <c r="R7" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="U7" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AD7" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.69</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.33</v>
+        <v>1.03</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46014.41666666666</v>
@@ -1475,30 +1475,30 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.5</v>
+        <v>7.12</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="N9" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="O9" t="n">
         <v>6</v>
@@ -1513,49 +1513,49 @@
         <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.94</v>
+        <v>3.16</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
         <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
         <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
         <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH9" t="n">
         <v>1.07</v>
